--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.00391697993473</v>
+        <v>2.600636509239393</v>
       </c>
       <c r="D2" t="n">
-        <v>9.521625807848769</v>
+        <v>1.547264193775425</v>
       </c>
       <c r="E2" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F2" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.07815119158807</v>
+        <v>3.100199568633062</v>
       </c>
       <c r="D3" t="n">
-        <v>13.39476007755568</v>
+        <v>2.176648512602799</v>
       </c>
       <c r="E3" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F3" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.67695804802403</v>
+        <v>3.522505682803906</v>
       </c>
       <c r="D4" t="n">
-        <v>21.56133101674841</v>
+        <v>3.503716290221616</v>
       </c>
       <c r="E4" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F4" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.21136987904084</v>
+        <v>3.771847605344136</v>
       </c>
       <c r="D5" t="n">
-        <v>23.19370555276162</v>
+        <v>3.768977152323763</v>
       </c>
       <c r="E5" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F5" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.10549119794785</v>
+        <v>4.729642319666526</v>
       </c>
       <c r="D6" t="n">
-        <v>29.44655484969066</v>
+        <v>4.785065163074733</v>
       </c>
       <c r="E6" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F6" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.66609728036907</v>
+        <v>8.720740808059974</v>
       </c>
       <c r="D7" t="n">
-        <v>53.03078193694451</v>
+        <v>8.617502064753483</v>
       </c>
       <c r="E7" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F7" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.88363193519322</v>
+        <v>8.106090189468899</v>
       </c>
       <c r="D8" t="n">
-        <v>50.42186855868605</v>
+        <v>8.193553640786483</v>
       </c>
       <c r="E8" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F8" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.71266260763526</v>
+        <v>9.37830767374073</v>
       </c>
       <c r="D9" t="n">
-        <v>56.91089872848606</v>
+        <v>9.248021043378985</v>
       </c>
       <c r="E9" t="n">
-        <v>15.96761975169696</v>
+        <v>2.594738209650756</v>
       </c>
       <c r="F9" t="n">
-        <v>17.48716141019561</v>
+        <v>2.841663729156787</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
